--- a/cds/mm_japan-5year-cds.xlsx
+++ b/cds/mm_japan-5year-cds.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="476">
   <si>
     <t>Date</t>
   </si>
@@ -1428,6 +1428,21 @@
   </si>
   <si>
     <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
   </si>
 </sst>
 </file>
@@ -1777,7 +1792,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B470"/>
+  <dimension ref="A1:B475"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -5538,6 +5553,46 @@
       </c>
       <c r="B470" s="3">
         <v>26.1635</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B471" s="3">
+        <v>27.8602</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B472" s="3">
+        <v>28.1291</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B473" s="3">
+        <v>29.6227</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B474" s="3">
+        <v>29.9986</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B475" s="3">
+        <v>28.8908</v>
       </c>
     </row>
   </sheetData>
